--- a/Inventory_Template.xlsx
+++ b/Inventory_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utexas-my.sharepoint.com/personal/aar5482_eid_utexas_edu/Documents/Desktop/MII tool 10092026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utexas-my.sharepoint.com/personal/aar5482_eid_utexas_edu/Documents/Downloads/mii/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="11_DC26603ED35D9E691189D01F5A90AEB2D4BFF0CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D1BA36F-2B1B-4F44-838F-0D5C2AFDDC62}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="11_DC26603ED35D9E691189D01F5A90AEB2D4BFF0CD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F2BE97D-40EE-4B5D-95C1-7211452BB5A8}"/>
   <bookViews>
-    <workbookView xWindow="-25695" yWindow="1350" windowWidth="25793" windowHeight="13875" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25695" yWindow="1350" windowWidth="25793" windowHeight="13875" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -350,7 +350,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="136">
   <si>
     <t>SHEETS:</t>
   </si>
@@ -409,9 +409,6 @@
     <t>measurement_date</t>
   </si>
   <si>
-    <t>method</t>
-  </si>
-  <si>
     <t>RPV_Op</t>
   </si>
   <si>
@@ -421,9 +418,6 @@
     <t>2024-06-01</t>
   </si>
   <si>
-    <t>Hi-Flow</t>
-  </si>
-  <si>
     <t>operating rod-packing</t>
   </si>
   <si>
@@ -466,9 +460,6 @@
     <t>TK-042-1</t>
   </si>
   <si>
-    <t>OGI + flow</t>
-  </si>
-  <si>
     <t>atmospheric tank</t>
   </si>
   <si>
@@ -529,18 +520,9 @@
     <t>overpass_datetime</t>
   </si>
   <si>
-    <t>provider</t>
-  </si>
-  <si>
-    <t>mdl_kgh</t>
-  </si>
-  <si>
     <t>2024-07-12 10:23</t>
   </si>
   <si>
-    <t>Bridger</t>
-  </si>
-  <si>
     <t>aerial, source attributed</t>
   </si>
   <si>
@@ -751,15 +733,6 @@
     <t xml:space="preserve">  BU_StackTests    —       Stack tests data (kg CH4 / mmbtu).</t>
   </si>
   <si>
-    <t xml:space="preserve">  BU_VentEmissions  —   Vents (RPV, WSV, DSV, BDV, ISO) measurements including zero rates, resolved by operational status (kg/hr).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BU_Tanks         —          Tank emissions measurements including zero rates (kg/hr).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  BU_Leaks         —           LDAR survey data including zero rates (kg/hr).</t>
-  </si>
-  <si>
     <t xml:space="preserve">  BU_Pneumatics    —       Malfunctioning pneumatics ONLY (kg/hr). Normally functioning devices use EPA factors and are NOT listed here.</t>
   </si>
   <si>
@@ -776,13 +749,22 @@
   </si>
   <si>
     <t xml:space="preserve">  Config           —              Optional overrides (n_resamples, random_state, survey_interval_hours, surveys_per_year).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BU_Leaks         —           LDAR survey data (kg/hr).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BU_Tanks         —          Tank emissions measurements including ZERO rates (kg/hr).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  BU_VentEmissions  —   Vents (RPV, WSV, DSV, BDV, ISO) measurements including ZERO rates, resolved by operational status (kg/hr).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -842,13 +824,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -895,25 +870,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -929,10 +902,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1228,339 +1197,343 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.649999999999999" x14ac:dyDescent="0.5">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="9"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A12" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A14" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A15" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A16" s="9"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A18" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A19" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A20" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A21" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A22" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A8" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A9" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A10" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A11" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A15" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A16" s="5"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A17" s="10" t="s">
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A25" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A26" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A27" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A28" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A18" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A19" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A20" s="7" t="s">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A29" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A31" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A32" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A33" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A21" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A22" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A23" s="9"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A24" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A25" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A26" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A27" s="7" t="s">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A34" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A28" s="7" t="s">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A35" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A29" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A31" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A32" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A33" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A34" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A35" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A15:F15"/>
@@ -1577,18 +1550,14 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1605,21 +1574,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>97</v>
+        <v>90</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
@@ -1633,10 +1602,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2">
         <v>20</v>
@@ -1647,10 +1616,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2">
         <v>25</v>
@@ -1661,10 +1630,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2">
         <v>15</v>
@@ -1675,10 +1644,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C6" s="2">
         <v>29</v>
@@ -1689,10 +1658,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2">
         <v>31</v>
@@ -1719,57 +1688,57 @@
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2">
         <v>9999</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2">
         <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2">
         <v>2160</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B5" s="2">
         <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1860,17 +1829,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="28" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -1884,110 +1852,92 @@
         <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="B2" s="2">
         <v>2.2999999999999998</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="B3" s="2">
         <v>0.4</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B4" s="2">
         <v>1.1000000000000001</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="B5" s="2">
         <v>0.8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2">
         <v>45.2</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1998,16 +1948,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -2018,43 +1966,34 @@
         <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>0.5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1.2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="D3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2078,10 +2017,10 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>18</v>
@@ -2095,16 +2034,16 @@
         <v>0.15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -2112,13 +2051,13 @@
         <v>0.42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -2127,16 +2066,16 @@
         <v>2.1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2159,10 +2098,10 @@
         <v>17</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>5</v>
@@ -2173,13 +2112,13 @@
         <v>0.85</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
@@ -2187,13 +2126,13 @@
         <v>1.85</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
@@ -2201,13 +2140,13 @@
         <v>0.42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2218,17 +2157,16 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
@@ -2236,106 +2174,76 @@
         <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>18.399999999999999</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F2" s="2">
-        <v>3</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B3" s="2">
         <v>6.1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F3" s="2">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+        <v>59</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B4" s="2">
         <v>12.5</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F4" s="2">
-        <v>3</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="B5" s="2">
         <v>4.2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F5" s="2">
-        <v>3</v>
-      </c>
-      <c r="G5" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="E5" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2359,45 +2267,45 @@
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
@@ -2417,16 +2325,16 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>10</v>
@@ -2446,16 +2354,16 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
@@ -2475,19 +2383,19 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2">
         <v>7900</v>
@@ -2504,16 +2412,16 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>10</v>
@@ -2555,42 +2463,42 @@
   <sheetData>
     <row r="1" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2">
         <v>1</v>
@@ -2623,7 +2531,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2">
         <v>1</v>
